--- a/docentes/Miguel Lopez Yadira - Estadisticos 20232.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="83">
   <si>
     <t>Mat</t>
   </si>
@@ -70,148 +70,199 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>CUAPIO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>SOSA</t>
   </si>
   <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>TREJO</t>
   </si>
   <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>FRANCISCO XAVIER</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>SAMIR</t>
   </si>
   <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
     <t>JOSUE</t>
   </si>
   <si>
-    <t>LUZ YESENIA</t>
+    <t>NURIA BELEN</t>
   </si>
   <si>
     <t>GISELA GUADALUPE</t>
   </si>
   <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>BRISEIDA</t>
+  </si>
+  <si>
     <t>FATIMA</t>
   </si>
   <si>
-    <t>OSCAR ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>FRANCISCO XAVIER</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>DORIAN</t>
   </si>
   <si>
     <t>VICTORIA VIANNEY</t>
@@ -706,16 +757,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.55</v>
+      </c>
+      <c r="H2">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -729,16 +783,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H3">
+        <v>9.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -865,16 +922,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920222</v>
+        <v>23330051920218</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -888,16 +945,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920318</v>
+        <v>23330051920230</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -911,22 +968,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920240</v>
+        <v>23330051920247</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -934,22 +991,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920244</v>
+        <v>23330051920258</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -957,22 +1014,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920328</v>
+        <v>23330051920265</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -980,16 +1037,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920260</v>
+        <v>23330051920226</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1003,16 +1060,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920278</v>
+        <v>23330051920244</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1026,39 +1083,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920221</v>
+        <v>23330051920333</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920223</v>
+        <v>23330051920221</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1072,16 +1129,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920247</v>
+        <v>23330051920223</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1095,22 +1152,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920213</v>
+        <v>22330051920404</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1118,22 +1175,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920227</v>
+        <v>23330051920318</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1141,16 +1198,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920239</v>
+        <v>23330051920213</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1164,16 +1221,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920256</v>
+        <v>23330051920227</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1187,16 +1244,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920257</v>
+        <v>23330051920242</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1210,16 +1267,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920330</v>
+        <v>23330051920240</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1233,16 +1290,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920270</v>
+        <v>23330051920239</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1256,24 +1313,185 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
+        <v>23330051920328</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920256</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920257</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920260</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920330</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920270</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920207</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
         <v>23330051920276</v>
       </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20232.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="121">
   <si>
     <t>Mat</t>
   </si>
@@ -70,13 +70,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
     <t>ALMANZA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>RAMIREZ</t>
@@ -85,42 +121,33 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MEJIA</t>
   </si>
   <si>
@@ -136,39 +163,72 @@
     <t>ROSALES</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>MENDEZ</t>
+    <t>GUZMAN</t>
   </si>
   <si>
     <t>BERMUDEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
+    <t>TEMOXTLE</t>
   </si>
   <si>
     <t>VILLA</t>
   </si>
   <si>
+    <t>FERRER</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
@@ -178,9 +238,6 @@
     <t>RICO</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>CANDELARIO</t>
   </si>
   <si>
@@ -190,63 +247,114 @@
     <t>TREJO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>MIREILLE</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
   </si>
   <si>
     <t>VANESA BETHSABE</t>
   </si>
   <si>
-    <t>JAIRO</t>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>FRANCISCO XAVIER</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
   </si>
   <si>
     <t>RAYMUNDO</t>
   </si>
   <si>
+    <t>SAMIR</t>
+  </si>
+  <si>
     <t>AIDE SCARLET</t>
   </si>
   <si>
     <t>KAREN</t>
   </si>
   <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
     <t>YAMILETH</t>
   </si>
   <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
     <t>LUZ YESENIA</t>
   </si>
   <si>
     <t>SILVANA</t>
   </si>
   <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>FRANCISCO XAVIER</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
+    <t>XIMENA ISABEL</t>
   </si>
   <si>
     <t>NURIA BELEN</t>
   </si>
   <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
     <t>DANNA PAOLA</t>
   </si>
   <si>
@@ -266,6 +374,12 @@
   </si>
   <si>
     <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -890,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -922,16 +1036,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920218</v>
+        <v>23330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -951,10 +1065,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -968,16 +1082,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920247</v>
+        <v>23330051920229</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -991,16 +1105,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920258</v>
+        <v>23330051920241</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1014,16 +1128,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920265</v>
+        <v>23330051920243</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1037,22 +1151,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920226</v>
+        <v>23330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1060,22 +1174,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920244</v>
+        <v>23330051920249</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1083,22 +1197,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920333</v>
+        <v>23330051920253</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1106,16 +1220,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920221</v>
+        <v>23330051920273</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1124,90 +1238,90 @@
         <v>9</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920223</v>
+        <v>23330051920191</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920404</v>
+        <v>23330051920328</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920318</v>
+        <v>23330051920357</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920213</v>
+        <v>23330051920280</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1216,27 +1330,27 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920227</v>
+        <v>23330051920218</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1244,22 +1358,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920242</v>
+        <v>23330051920221</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1267,22 +1381,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920240</v>
+        <v>23330051920223</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1290,22 +1404,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920239</v>
+        <v>22330051920404</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1313,22 +1427,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920328</v>
+        <v>23330051920228</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1336,22 +1450,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920256</v>
+        <v>23330051920245</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1359,22 +1473,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920257</v>
+        <v>23330051920247</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1382,22 +1496,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920260</v>
+        <v>23330051920318</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1405,22 +1519,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920330</v>
+        <v>23330051920258</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1428,22 +1542,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920270</v>
+        <v>23330051920265</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1451,16 +1565,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920207</v>
+        <v>23330051920213</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1474,24 +1588,461 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
+        <v>23330051920226</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920215</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920227</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920237</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920242</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>23330051920240</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>23330051920244</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>23330051920333</v>
+      </c>
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>23330051920252</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>23330051920239</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>23330051920256</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" t="s">
+        <v>112</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>23330051920257</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>23330051920260</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>23330051920330</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>23330051920270</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>23330051920207</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>23330051920327</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" t="s">
+        <v>105</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
         <v>23330051920276</v>
       </c>
-      <c r="B26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26">
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>23330051920278</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>23330051920277</v>
+      </c>
+      <c r="B45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" t="s">
+        <v>120</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20232.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Mat</t>
   </si>
@@ -68,42 +68,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
   </si>
 </sst>
 </file>
@@ -689,16 +653,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>68.97</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -715,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>87.88</v>
+        <v>90.91</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -764,98 +728,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920243</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920335</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920228</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920247</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
